--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="16275" windowHeight="15945"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -275,6 +275,126 @@
   </si>
   <si>
     <t>5010</t>
+  </si>
+  <si>
+    <t>6001</t>
+  </si>
+  <si>
+    <t>6002</t>
+  </si>
+  <si>
+    <t>6003</t>
+  </si>
+  <si>
+    <t>6004</t>
+  </si>
+  <si>
+    <t>6005</t>
+  </si>
+  <si>
+    <t>6006</t>
+  </si>
+  <si>
+    <t>6007</t>
+  </si>
+  <si>
+    <t>6008</t>
+  </si>
+  <si>
+    <t>6009</t>
+  </si>
+  <si>
+    <t>6010</t>
+  </si>
+  <si>
+    <t>7001</t>
+  </si>
+  <si>
+    <t>7002</t>
+  </si>
+  <si>
+    <t>7003</t>
+  </si>
+  <si>
+    <t>7004</t>
+  </si>
+  <si>
+    <t>7005</t>
+  </si>
+  <si>
+    <t>7006</t>
+  </si>
+  <si>
+    <t>7007</t>
+  </si>
+  <si>
+    <t>7008</t>
+  </si>
+  <si>
+    <t>7009</t>
+  </si>
+  <si>
+    <t>7010</t>
+  </si>
+  <si>
+    <t>8001</t>
+  </si>
+  <si>
+    <t>8002</t>
+  </si>
+  <si>
+    <t>8003</t>
+  </si>
+  <si>
+    <t>8004</t>
+  </si>
+  <si>
+    <t>8005</t>
+  </si>
+  <si>
+    <t>8006</t>
+  </si>
+  <si>
+    <t>8007</t>
+  </si>
+  <si>
+    <t>8008</t>
+  </si>
+  <si>
+    <t>8009</t>
+  </si>
+  <si>
+    <t>8010</t>
+  </si>
+  <si>
+    <t>9001</t>
+  </si>
+  <si>
+    <t>9002</t>
+  </si>
+  <si>
+    <t>9003</t>
+  </si>
+  <si>
+    <t>9004</t>
+  </si>
+  <si>
+    <t>9005</t>
+  </si>
+  <si>
+    <t>9006</t>
+  </si>
+  <si>
+    <t>9007</t>
+  </si>
+  <si>
+    <t>9008</t>
+  </si>
+  <si>
+    <t>9009</t>
+  </si>
+  <si>
+    <t>9010</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1368,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2019,6 +2139,566 @@
         <v>40</v>
       </c>
     </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="B66" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="B73" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="B74" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="B75" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="B76" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="B78" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5">
+      <c r="B79" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5">
+      <c r="B80" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="B82" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5">
+      <c r="B83" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="B86" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="B93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5">
+      <c r="B94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5">
+      <c r="B95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5">
+      <c r="B96" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="B98" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="B99" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="B100" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16275" windowHeight="15945"/>
+    <workbookView windowWidth="18270" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -73,91 +73,91 @@
     <t>1</t>
   </si>
   <si>
+    <t>10071|10072|10073</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10031</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10041|10042</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10051|10052</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10061|10062</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10081|10082|10083</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10091|10092|10093</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10101|10102|10103</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>10011</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10021</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10031</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10041|10042</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10051|10052</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10061|10062</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10071|10072|10073</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10081|10082|10083</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10091|10092|10093</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10101|10102|10103</t>
-  </si>
-  <si>
-    <t>2001</t>
   </si>
   <si>
     <t>2002</t>
@@ -1534,54 +1534,54 @@
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>15</v>
@@ -1590,7 +1590,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1674,7 +1674,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -1685,10 +1685,10 @@
         <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -1699,10 +1699,10 @@
         <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1713,10 +1713,10 @@
         <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1730,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -1814,7 +1814,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="2:5">
@@ -1825,10 +1825,10 @@
         <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="35" spans="2:5">
@@ -1839,10 +1839,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:5">
@@ -1853,10 +1853,10 @@
         <v>18</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="38" spans="2:5">
@@ -1870,7 +1870,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="2:5">
@@ -1954,7 +1954,7 @@
         <v>30</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:5">
@@ -1965,10 +1965,10 @@
         <v>21</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:5">
@@ -1979,10 +1979,10 @@
         <v>21</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="47" spans="2:5">
@@ -1993,10 +1993,10 @@
         <v>21</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="49" spans="2:5">
@@ -2010,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="2:5">
@@ -2094,7 +2094,7 @@
         <v>30</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="2:5">
@@ -2105,10 +2105,10 @@
         <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:5">
@@ -2119,10 +2119,10 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:5">
@@ -2133,10 +2133,10 @@
         <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="60" spans="2:5">
@@ -2150,7 +2150,7 @@
         <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="2:5">
@@ -2234,7 +2234,7 @@
         <v>30</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="2:5">
@@ -2245,10 +2245,10 @@
         <v>27</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="68" spans="2:5">
@@ -2259,10 +2259,10 @@
         <v>27</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="69" spans="2:5">
@@ -2273,10 +2273,10 @@
         <v>27</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -2290,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="2:5">
@@ -2374,7 +2374,7 @@
         <v>30</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="2:5">
@@ -2385,10 +2385,10 @@
         <v>30</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="79" spans="2:5">
@@ -2399,10 +2399,10 @@
         <v>30</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="80" spans="2:5">
@@ -2413,10 +2413,10 @@
         <v>30</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="82" spans="2:5">
@@ -2424,13 +2424,13 @@
         <v>101</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="2:5">
@@ -2438,7 +2438,7 @@
         <v>102</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>15</v>
@@ -2452,7 +2452,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>18</v>
@@ -2466,7 +2466,7 @@
         <v>104</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>21</v>
@@ -2480,7 +2480,7 @@
         <v>105</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>24</v>
@@ -2494,7 +2494,7 @@
         <v>106</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>27</v>
@@ -2508,13 +2508,13 @@
         <v>107</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="2:5">
@@ -2522,13 +2522,13 @@
         <v>108</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="90" spans="2:5">
@@ -2536,13 +2536,13 @@
         <v>109</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="91" spans="2:5">
@@ -2550,13 +2550,13 @@
         <v>110</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="93" spans="2:5">
@@ -2564,13 +2564,13 @@
         <v>111</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94" spans="2:5">
@@ -2578,7 +2578,7 @@
         <v>112</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>15</v>
@@ -2592,7 +2592,7 @@
         <v>113</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>18</v>
@@ -2606,7 +2606,7 @@
         <v>114</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
@@ -2620,7 +2620,7 @@
         <v>115</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>24</v>
@@ -2634,7 +2634,7 @@
         <v>116</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>27</v>
@@ -2648,13 +2648,13 @@
         <v>117</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="2:5">
@@ -2662,13 +2662,13 @@
         <v>118</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="101" spans="2:5">
@@ -2676,13 +2676,13 @@
         <v>119</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="102" spans="2:5">
@@ -2690,13 +2690,13 @@
         <v>120</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="13050"/>
+    <workbookView windowWidth="18270" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -73,94 +73,94 @@
     <t>1</t>
   </si>
   <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10101|10102|10103</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10031</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10041|10042</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10051|10052</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10061|10062</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>10071|10072|10073</t>
   </si>
   <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10081|10082|10083</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10091|10092|10093</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
   </si>
   <si>
     <t>10021</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10031</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10041|10042</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10051|10052</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10061|10062</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10081|10082|10083</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10091|10092|10093</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10101|10102|10103</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>10011</t>
-  </si>
-  <si>
-    <t>2002</t>
   </si>
   <si>
     <t>2003</t>
@@ -1534,49 +1534,49 @@
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1590,12 +1590,12 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>15</v>
@@ -1604,7 +1604,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1674,7 +1674,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -1685,10 +1685,10 @@
         <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -1699,10 +1699,10 @@
         <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1713,10 +1713,10 @@
         <v>15</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1730,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -1744,7 +1744,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -1814,7 +1814,7 @@
         <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:5">
@@ -1825,10 +1825,10 @@
         <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="2:5">
@@ -1839,10 +1839,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="2:5">
@@ -1853,10 +1853,10 @@
         <v>18</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="2:5">
@@ -1870,7 +1870,7 @@
         <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="2:5">
@@ -1884,7 +1884,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="2:5">
@@ -1954,7 +1954,7 @@
         <v>30</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:5">
@@ -1965,10 +1965,10 @@
         <v>21</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:5">
@@ -1979,10 +1979,10 @@
         <v>21</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="2:5">
@@ -1993,10 +1993,10 @@
         <v>21</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="2:5">
@@ -2010,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:5">
@@ -2024,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="2:5">
@@ -2094,7 +2094,7 @@
         <v>30</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:5">
@@ -2105,10 +2105,10 @@
         <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:5">
@@ -2119,10 +2119,10 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:5">
@@ -2133,10 +2133,10 @@
         <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="2:5">
@@ -2150,7 +2150,7 @@
         <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="2:5">
@@ -2164,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="2:5">
@@ -2234,7 +2234,7 @@
         <v>30</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="2:5">
@@ -2245,10 +2245,10 @@
         <v>27</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="2:5">
@@ -2259,10 +2259,10 @@
         <v>27</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="2:5">
@@ -2273,10 +2273,10 @@
         <v>27</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -2290,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="2:5">
@@ -2304,7 +2304,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="2:5">
@@ -2374,7 +2374,7 @@
         <v>30</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="2:5">
@@ -2385,10 +2385,10 @@
         <v>30</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="2:5">
@@ -2399,10 +2399,10 @@
         <v>30</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="2:5">
@@ -2413,10 +2413,10 @@
         <v>30</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="2:5">
@@ -2424,13 +2424,13 @@
         <v>101</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="2:5">
@@ -2438,13 +2438,13 @@
         <v>102</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="2:5">
@@ -2452,7 +2452,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>18</v>
@@ -2466,7 +2466,7 @@
         <v>104</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>21</v>
@@ -2480,7 +2480,7 @@
         <v>105</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>24</v>
@@ -2494,7 +2494,7 @@
         <v>106</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>27</v>
@@ -2508,13 +2508,13 @@
         <v>107</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="2:5">
@@ -2522,13 +2522,13 @@
         <v>108</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="2:5">
@@ -2536,13 +2536,13 @@
         <v>109</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="2:5">
@@ -2550,13 +2550,13 @@
         <v>110</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="2:5">
@@ -2564,13 +2564,13 @@
         <v>111</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="2:5">
@@ -2578,13 +2578,13 @@
         <v>112</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="2:5">
@@ -2592,7 +2592,7 @@
         <v>113</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>18</v>
@@ -2606,7 +2606,7 @@
         <v>114</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>21</v>
@@ -2620,7 +2620,7 @@
         <v>115</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>24</v>
@@ -2634,7 +2634,7 @@
         <v>116</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>27</v>
@@ -2648,13 +2648,13 @@
         <v>117</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="2:5">
@@ -2662,13 +2662,13 @@
         <v>118</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="2:5">
@@ -2676,13 +2676,13 @@
         <v>119</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="102" spans="2:5">
@@ -2690,13 +2690,13 @@
         <v>120</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="14775"/>
+    <workbookView windowWidth="9660" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -82,85 +82,85 @@
     <t>2</t>
   </si>
   <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10031</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10041|10042</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10051|10052</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10061|10062</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10071|10072|10073</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10081|10082|10083</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10091|10092|10093</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>10101|10102|10103</t>
   </si>
   <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10031</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10041|10042</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10051|10052</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10061|10062</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10071|10072|10073</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10081|10082|10083</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10091|10092|10093</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
     <t>2002</t>
-  </si>
-  <si>
-    <t>10021</t>
   </si>
   <si>
     <t>2003</t>
@@ -1576,12 +1576,12 @@
         <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>15</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>15</v>
@@ -1604,7 +1604,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1716,7 +1716,7 @@
         <v>39</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1744,7 +1744,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -1856,7 +1856,7 @@
         <v>39</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="2:5">
@@ -1884,7 +1884,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="2:5">
@@ -1996,7 +1996,7 @@
         <v>39</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="2:5">
@@ -2024,7 +2024,7 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="2:5">
@@ -2136,7 +2136,7 @@
         <v>39</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="2:5">
@@ -2164,7 +2164,7 @@
         <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="2:5">
@@ -2276,7 +2276,7 @@
         <v>39</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="2:5">
@@ -2304,7 +2304,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="2:5">
@@ -2416,7 +2416,7 @@
         <v>39</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82" spans="2:5">
@@ -2444,7 +2444,7 @@
         <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="2:5">
@@ -2556,7 +2556,7 @@
         <v>39</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" spans="2:5">
@@ -2584,7 +2584,7 @@
         <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="2:5">
@@ -2696,7 +2696,7 @@
         <v>39</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="9660" windowHeight="14775"/>
+    <workbookView windowWidth="10350" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10350" windowHeight="14775"/>
+    <workbookView windowWidth="9270" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -160,31 +160,61 @@
     <t>2001</t>
   </si>
   <si>
+    <t>20011</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
+    <t>20021</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
+    <t>20031</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
+    <t>20041|20042</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
+    <t>20051|20052</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
+    <t>20061|20062</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
+    <t>20071|20072|20073</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
+    <t>20081|20082|20083</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
+    <t>20091|20092|20093</t>
+  </si>
+  <si>
     <t>2010</t>
+  </si>
+  <si>
+    <t>20101|20102|20103</t>
   </si>
   <si>
     <t>3001</t>
@@ -1590,12 +1620,12 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>15</v>
@@ -1604,12 +1634,12 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>15</v>
@@ -1618,12 +1648,12 @@
         <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>15</v>
@@ -1632,12 +1662,12 @@
         <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>15</v>
@@ -1646,12 +1676,12 @@
         <v>24</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>15</v>
@@ -1660,12 +1690,12 @@
         <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>15</v>
@@ -1674,12 +1704,12 @@
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>15</v>
@@ -1688,12 +1718,12 @@
         <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
@@ -1702,12 +1732,12 @@
         <v>36</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>15</v>
@@ -1716,12 +1746,12 @@
         <v>39</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
@@ -1735,7 +1765,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -1749,7 +1779,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -1763,7 +1793,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -1777,7 +1807,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
@@ -1791,7 +1821,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>18</v>
@@ -1805,7 +1835,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
@@ -1819,7 +1849,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -1833,7 +1863,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -1847,7 +1877,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
@@ -1861,7 +1891,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>21</v>
@@ -1875,7 +1905,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>21</v>
@@ -1889,7 +1919,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>21</v>
@@ -1903,7 +1933,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>21</v>
@@ -1917,7 +1947,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>21</v>
@@ -1931,7 +1961,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>21</v>
@@ -1945,7 +1975,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>21</v>
@@ -1959,7 +1989,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>21</v>
@@ -1973,7 +2003,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>21</v>
@@ -1987,7 +2017,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>21</v>
@@ -2001,7 +2031,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>24</v>
@@ -2015,7 +2045,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>24</v>
@@ -2029,7 +2059,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>24</v>
@@ -2043,7 +2073,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>24</v>
@@ -2057,7 +2087,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>24</v>
@@ -2071,7 +2101,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>24</v>
@@ -2085,7 +2115,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>24</v>
@@ -2099,7 +2129,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>24</v>
@@ -2113,7 +2143,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>24</v>
@@ -2127,7 +2157,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>24</v>
@@ -2141,7 +2171,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>27</v>
@@ -2155,7 +2185,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>27</v>
@@ -2169,7 +2199,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>27</v>
@@ -2183,7 +2213,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>27</v>
@@ -2197,7 +2227,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>27</v>
@@ -2211,7 +2241,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>27</v>
@@ -2225,7 +2255,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>27</v>
@@ -2239,7 +2269,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>27</v>
@@ -2253,7 +2283,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>27</v>
@@ -2267,7 +2297,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>27</v>
@@ -2281,7 +2311,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>30</v>
@@ -2295,7 +2325,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>30</v>
@@ -2309,7 +2339,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>30</v>
@@ -2323,7 +2353,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>30</v>
@@ -2337,7 +2367,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>30</v>
@@ -2351,7 +2381,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>30</v>
@@ -2365,7 +2395,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>30</v>
@@ -2379,7 +2409,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>30</v>
@@ -2393,7 +2423,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>30</v>
@@ -2407,7 +2437,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="1" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>30</v>
@@ -2421,7 +2451,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>33</v>
@@ -2435,7 +2465,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="1" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>33</v>
@@ -2449,7 +2479,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>33</v>
@@ -2463,7 +2493,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>33</v>
@@ -2477,7 +2507,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>33</v>
@@ -2491,7 +2521,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>33</v>
@@ -2505,7 +2535,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>33</v>
@@ -2519,7 +2549,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>33</v>
@@ -2533,7 +2563,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>33</v>
@@ -2547,7 +2577,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>33</v>
@@ -2561,7 +2591,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>36</v>
@@ -2575,7 +2605,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>36</v>
@@ -2589,7 +2619,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>36</v>
@@ -2603,7 +2633,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>36</v>
@@ -2617,7 +2647,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>36</v>
@@ -2631,7 +2661,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>36</v>
@@ -2645,7 +2675,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>36</v>
@@ -2659,7 +2689,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>36</v>
@@ -2673,7 +2703,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>36</v>
@@ -2687,7 +2717,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>36</v>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="9270" windowHeight="14775"/>
+    <workbookView windowWidth="10875" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -49,6 +49,9 @@
     <t>MonsterGroup</t>
   </si>
   <si>
+    <t>GetGold</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>怪物组id</t>
   </si>
   <si>
+    <t>通关金币</t>
+  </si>
+  <si>
     <t>1001</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>10011</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>1002</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>10041|10042</t>
   </si>
   <si>
+    <t>55</t>
+  </si>
+  <si>
     <t>1005</t>
   </si>
   <si>
@@ -128,6 +140,9 @@
   </si>
   <si>
     <t>10071|10072|10073</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
   <si>
     <t>1008</t>
@@ -1427,1306 +1442,1555 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F49" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="1" t="s">
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="F60" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="E61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="B65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="B66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="B67" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="B68" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="F71" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="B73" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="E73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="B74" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="B75" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
+      <c r="B76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
+      <c r="B77" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
+      <c r="B78" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
+      <c r="B79" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
+      <c r="B80" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
+      <c r="B82" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="F82" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6">
+      <c r="B83" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
+      <c r="B84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
+      <c r="B85" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6">
+      <c r="B86" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6">
+      <c r="B87" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6">
+      <c r="B88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6">
+      <c r="B89" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
+      <c r="B90" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6">
+      <c r="B91" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
+      <c r="B93" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="F93" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6">
+      <c r="B94" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
+      <c r="B95" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
+      <c r="B96" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
+      <c r="B99" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="1" t="s">
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="B43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="1" t="s">
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5">
-      <c r="B55" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5">
-      <c r="B56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5">
-      <c r="B60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5">
-      <c r="B61" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="B62" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5">
-      <c r="B63" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5">
-      <c r="B65" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5">
-      <c r="B66" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5">
-      <c r="B68" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5">
-      <c r="B69" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5">
-      <c r="B71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5">
-      <c r="B72" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5">
-      <c r="B73" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5">
-      <c r="B74" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5">
-      <c r="B75" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5">
-      <c r="B76" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5">
-      <c r="B77" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5">
-      <c r="B78" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5">
-      <c r="B79" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5">
-      <c r="B80" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5">
-      <c r="B82" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5">
-      <c r="B83" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5">
-      <c r="B84" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5">
-      <c r="B85" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5">
-      <c r="B86" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5">
-      <c r="B87" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5">
-      <c r="B88" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5">
-      <c r="B89" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5">
-      <c r="B90" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5">
-      <c r="B91" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5">
-      <c r="B93" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5">
-      <c r="B94" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5">
-      <c r="B95" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5">
-      <c r="B96" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5">
-      <c r="B97" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5">
-      <c r="B98" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5">
-      <c r="B99" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5">
-      <c r="B100" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5">
-      <c r="B101" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5">
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10875" windowHeight="9750"/>
+    <workbookView windowWidth="16065" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16065" windowHeight="9750"/>
+    <workbookView windowWidth="12450" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -82,7 +82,7 @@
     <t>10011</t>
   </si>
   <si>
-    <t>40</t>
+    <t>60</t>
   </si>
   <si>
     <t>1002</t>
@@ -94,6 +94,9 @@
     <t>10021</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
     <t>1003</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>10031</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>1004</t>
   </si>
   <si>
@@ -112,7 +118,7 @@
     <t>10041|10042</t>
   </si>
   <si>
-    <t>55</t>
+    <t>120</t>
   </si>
   <si>
     <t>1005</t>
@@ -124,6 +130,9 @@
     <t>10051|10052</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>1006</t>
   </si>
   <si>
@@ -133,6 +142,9 @@
     <t>10061|10062</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>1007</t>
   </si>
   <si>
@@ -142,7 +154,7 @@
     <t>10071|10072|10073</t>
   </si>
   <si>
-    <t>70</t>
+    <t>180</t>
   </si>
   <si>
     <t>1008</t>
@@ -154,6 +166,9 @@
     <t>10081|10082|10083</t>
   </si>
   <si>
+    <t>200</t>
+  </si>
+  <si>
     <t>1009</t>
   </si>
   <si>
@@ -161,6 +176,9 @@
   </si>
   <si>
     <t>10091|10092|10093</t>
+  </si>
+  <si>
+    <t>220</t>
   </si>
   <si>
     <t>1010</t>
@@ -1520,146 +1538,146 @@
         <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1668,7 +1686,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>16</v>
@@ -1676,7 +1694,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
@@ -1685,151 +1703,151 @@
         <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
@@ -1843,10 +1861,10 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>18</v>
@@ -1855,148 +1873,148 @@
         <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>14</v>
@@ -2010,10 +2028,10 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>18</v>
@@ -2022,148 +2040,148 @@
         <v>19</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>14</v>
@@ -2177,10 +2195,10 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>18</v>
@@ -2189,148 +2207,148 @@
         <v>19</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>14</v>
@@ -2344,10 +2362,10 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>18</v>
@@ -2356,148 +2374,148 @@
         <v>19</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F64" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>14</v>
@@ -2511,10 +2529,10 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>18</v>
@@ -2523,148 +2541,148 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>14</v>
@@ -2678,10 +2696,10 @@
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>18</v>
@@ -2690,148 +2708,148 @@
         <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>14</v>
@@ -2845,10 +2863,10 @@
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>18</v>
@@ -2857,140 +2875,140 @@
         <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12450" windowHeight="9750"/>
+    <workbookView windowWidth="7740" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1431,15 +1431,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="9.01666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="24.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.65" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.53333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.675" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.0166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="34.75" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
@@ -2020,7 +2020,7 @@
         <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>16</v>
@@ -2037,7 +2037,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>20</v>
@@ -2054,7 +2054,7 @@
         <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>24</v>
@@ -2071,7 +2071,7 @@
         <v>26</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>28</v>
@@ -2088,7 +2088,7 @@
         <v>30</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>32</v>
@@ -2105,7 +2105,7 @@
         <v>34</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>36</v>
@@ -2122,7 +2122,7 @@
         <v>38</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>40</v>
@@ -2139,7 +2139,7 @@
         <v>42</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>44</v>
@@ -2156,7 +2156,7 @@
         <v>46</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>48</v>
@@ -2173,7 +2173,7 @@
         <v>50</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2354,7 +2354,7 @@
         <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>16</v>
@@ -2371,7 +2371,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>20</v>
@@ -2388,7 +2388,7 @@
         <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>24</v>
@@ -2405,7 +2405,7 @@
         <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>30</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>32</v>
@@ -2439,7 +2439,7 @@
         <v>34</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>36</v>
@@ -2456,7 +2456,7 @@
         <v>38</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>40</v>
@@ -2473,7 +2473,7 @@
         <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>44</v>
@@ -2490,7 +2490,7 @@
         <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>48</v>
@@ -2507,7 +2507,7 @@
         <v>50</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -2688,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>16</v>
@@ -2705,7 +2705,7 @@
         <v>18</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>20</v>
@@ -2722,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>24</v>
@@ -2739,7 +2739,7 @@
         <v>26</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>28</v>
@@ -2756,7 +2756,7 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>32</v>
@@ -2773,7 +2773,7 @@
         <v>34</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>36</v>
@@ -2790,7 +2790,7 @@
         <v>38</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>40</v>
@@ -2807,7 +2807,7 @@
         <v>42</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>44</v>
@@ -2824,7 +2824,7 @@
         <v>46</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>48</v>
@@ -2841,7 +2841,7 @@
         <v>50</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="2:6">
@@ -3010,6 +3010,36 @@
       <c r="E102" s="1" t="s">
         <v>51</v>
       </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="E104"/>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="E105"/>
+    </row>
+    <row r="106" spans="2:6">
+      <c r="E106"/>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="E107"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="E108"/>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="E109"/>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="E110"/>
+    </row>
+    <row r="111" spans="2:6">
+      <c r="E111"/>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="5:5">
+      <c r="E113"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14415" windowHeight="11400"/>
+    <workbookView windowWidth="17820" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>10021|10102</t>
+    <t>10021</t>
   </si>
   <si>
     <t>1003</t>
@@ -1674,7 +1674,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="5.65" style="1" customWidth="1"/>
@@ -3175,7 +3175,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="97" spans="2:6">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
         <v>191</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="98" spans="2:6">
+    <row r="98" spans="1:6">
       <c r="B98" s="1" t="s">
         <v>193</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="99" spans="2:6">
+    <row r="99" spans="1:6">
       <c r="B99" s="1" t="s">
         <v>195</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="1:6">
       <c r="B100" s="1" t="s">
         <v>197</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="1:6">
       <c r="B101" s="1" t="s">
         <v>199</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="1:6">
       <c r="B102" s="1" t="s">
         <v>201</v>
       </c>
@@ -3277,393 +3277,363 @@
         <v>530</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
-      <c r="E104"/>
-    </row>
-    <row r="105" spans="2:6">
-      <c r="E105"/>
-    </row>
-    <row r="106" spans="2:6">
-      <c r="E106"/>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="E107"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="E108"/>
-    </row>
-    <row r="109" spans="2:6">
-      <c r="E109"/>
-    </row>
-    <row r="110" spans="2:6">
-      <c r="E110"/>
-    </row>
-    <row r="111" spans="2:6">
-      <c r="E111"/>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="E112"/>
+    <row r="104" spans="1:6">
+      <c r="A104"/>
+      <c r="B104" s="2">
+        <v>10001</v>
+      </c>
+      <c r="C104" s="2">
+        <v>10</v>
+      </c>
+      <c r="D104" s="2">
+        <v>1</v>
+      </c>
+      <c r="E104" t="s">
+        <v>203</v>
+      </c>
+      <c r="F104" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105"/>
+      <c r="B105" s="2">
+        <v>10002</v>
+      </c>
+      <c r="C105" s="2">
+        <v>10</v>
+      </c>
+      <c r="D105" s="2">
+        <v>2</v>
+      </c>
+      <c r="E105" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106"/>
+      <c r="B106" s="2">
+        <v>10003</v>
+      </c>
+      <c r="C106" s="2">
+        <v>10</v>
+      </c>
+      <c r="D106" s="2">
+        <v>3</v>
+      </c>
+      <c r="E106" t="s">
+        <v>205</v>
+      </c>
+      <c r="F106" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107"/>
+      <c r="B107" s="2">
+        <v>10004</v>
+      </c>
+      <c r="C107" s="2">
+        <v>10</v>
+      </c>
+      <c r="D107" s="2">
+        <v>4</v>
+      </c>
+      <c r="E107" t="s">
+        <v>206</v>
+      </c>
+      <c r="F107" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108"/>
+      <c r="B108" s="2">
+        <v>10005</v>
+      </c>
+      <c r="C108" s="2">
+        <v>10</v>
+      </c>
+      <c r="D108" s="2">
+        <v>5</v>
+      </c>
+      <c r="E108" t="s">
+        <v>207</v>
+      </c>
+      <c r="F108" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109"/>
+      <c r="B109" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C109" s="2">
+        <v>10</v>
+      </c>
+      <c r="D109" s="2">
+        <v>6</v>
+      </c>
+      <c r="E109" t="s">
+        <v>208</v>
+      </c>
+      <c r="F109" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110"/>
+      <c r="B110" s="2">
+        <v>10007</v>
+      </c>
+      <c r="C110" s="2">
+        <v>10</v>
+      </c>
+      <c r="D110" s="2">
+        <v>7</v>
+      </c>
+      <c r="E110" t="s">
+        <v>209</v>
+      </c>
+      <c r="F110" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111"/>
+      <c r="B111" s="2">
+        <v>10008</v>
+      </c>
+      <c r="C111" s="2">
+        <v>10</v>
+      </c>
+      <c r="D111" s="2">
+        <v>8</v>
+      </c>
+      <c r="E111" t="s">
+        <v>210</v>
+      </c>
+      <c r="F111" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112"/>
+      <c r="B112" s="2">
+        <v>10009</v>
+      </c>
+      <c r="C112" s="2">
+        <v>10</v>
+      </c>
+      <c r="D112" s="2">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
+        <v>211</v>
+      </c>
+      <c r="F112" s="2">
+        <v>515</v>
+      </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="E113"/>
+      <c r="A113"/>
+      <c r="B113" s="2">
+        <v>10010</v>
+      </c>
+      <c r="C113" s="2">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2">
+        <v>10</v>
+      </c>
+      <c r="E113" t="s">
+        <v>212</v>
+      </c>
+      <c r="F113" s="2">
+        <v>565</v>
+      </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115"/>
-      <c r="B115">
-        <v>10001</v>
-      </c>
-      <c r="C115">
-        <v>10</v>
-      </c>
-      <c r="D115">
+      <c r="B115" s="2">
+        <v>11001</v>
+      </c>
+      <c r="C115" s="2">
+        <v>11</v>
+      </c>
+      <c r="D115" s="2">
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F115" s="2">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116"/>
-      <c r="B116">
-        <v>10002</v>
-      </c>
-      <c r="C116">
-        <v>10</v>
-      </c>
-      <c r="D116">
+      <c r="B116" s="2">
+        <v>11002</v>
+      </c>
+      <c r="C116" s="2">
+        <v>11</v>
+      </c>
+      <c r="D116" s="2">
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F116" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117"/>
-      <c r="B117">
-        <v>10003</v>
-      </c>
-      <c r="C117">
-        <v>10</v>
-      </c>
-      <c r="D117">
+      <c r="B117" s="2">
+        <v>11003</v>
+      </c>
+      <c r="C117" s="2">
+        <v>11</v>
+      </c>
+      <c r="D117" s="2">
         <v>3</v>
       </c>
       <c r="E117" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F117" s="2">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118"/>
-      <c r="B118">
-        <v>10004</v>
-      </c>
-      <c r="C118">
-        <v>10</v>
-      </c>
-      <c r="D118">
+      <c r="B118" s="2">
+        <v>11004</v>
+      </c>
+      <c r="C118" s="2">
+        <v>11</v>
+      </c>
+      <c r="D118" s="2">
         <v>4</v>
       </c>
       <c r="E118" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F118" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119"/>
-      <c r="B119">
-        <v>10005</v>
-      </c>
-      <c r="C119">
-        <v>10</v>
-      </c>
-      <c r="D119">
+      <c r="B119" s="2">
+        <v>11005</v>
+      </c>
+      <c r="C119" s="2">
+        <v>11</v>
+      </c>
+      <c r="D119" s="2">
         <v>5</v>
       </c>
       <c r="E119" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F119" s="2">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120"/>
-      <c r="B120">
-        <v>10006</v>
-      </c>
-      <c r="C120">
-        <v>10</v>
-      </c>
-      <c r="D120">
+      <c r="B120" s="2">
+        <v>11006</v>
+      </c>
+      <c r="C120" s="2">
+        <v>11</v>
+      </c>
+      <c r="D120" s="2">
         <v>6</v>
       </c>
       <c r="E120" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F120" s="2">
-        <v>375</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121"/>
-      <c r="B121">
-        <v>10007</v>
-      </c>
-      <c r="C121">
-        <v>10</v>
-      </c>
-      <c r="D121">
+      <c r="B121" s="2">
+        <v>11007</v>
+      </c>
+      <c r="C121" s="2">
+        <v>11</v>
+      </c>
+      <c r="D121" s="2">
         <v>7</v>
       </c>
       <c r="E121" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F121" s="2">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122"/>
-      <c r="B122">
-        <v>10008</v>
-      </c>
-      <c r="C122">
-        <v>10</v>
-      </c>
-      <c r="D122">
+      <c r="B122" s="2">
+        <v>11008</v>
+      </c>
+      <c r="C122" s="2">
+        <v>11</v>
+      </c>
+      <c r="D122" s="2">
         <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F122" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123"/>
-      <c r="B123">
-        <v>10009</v>
-      </c>
-      <c r="C123">
-        <v>10</v>
-      </c>
-      <c r="D123">
+      <c r="B123" s="2">
+        <v>11009</v>
+      </c>
+      <c r="C123" s="2">
+        <v>11</v>
+      </c>
+      <c r="D123" s="2">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F123" s="2">
-        <v>515</v>
+        <v>550</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124"/>
-      <c r="B124">
-        <v>10010</v>
-      </c>
-      <c r="C124">
+      <c r="B124" s="2">
+        <v>11010</v>
+      </c>
+      <c r="C124" s="2">
+        <v>11</v>
+      </c>
+      <c r="D124" s="2">
         <v>10</v>
       </c>
-      <c r="D124">
-        <v>10</v>
-      </c>
       <c r="E124" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F124" s="2">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126"/>
-      <c r="B126">
-        <v>11001</v>
-      </c>
-      <c r="C126">
-        <v>11</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126" t="s">
-        <v>213</v>
-      </c>
-      <c r="F126" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127"/>
-      <c r="B127">
-        <v>11002</v>
-      </c>
-      <c r="C127">
-        <v>11</v>
-      </c>
-      <c r="D127">
-        <v>2</v>
-      </c>
-      <c r="E127" t="s">
-        <v>214</v>
-      </c>
-      <c r="F127" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128"/>
-      <c r="B128">
-        <v>11003</v>
-      </c>
-      <c r="C128">
-        <v>11</v>
-      </c>
-      <c r="D128">
-        <v>3</v>
-      </c>
-      <c r="E128" t="s">
-        <v>215</v>
-      </c>
-      <c r="F128" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129"/>
-      <c r="B129">
-        <v>11004</v>
-      </c>
-      <c r="C129">
-        <v>11</v>
-      </c>
-      <c r="D129">
-        <v>4</v>
-      </c>
-      <c r="E129" t="s">
-        <v>216</v>
-      </c>
-      <c r="F129" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130"/>
-      <c r="B130">
-        <v>11005</v>
-      </c>
-      <c r="C130">
-        <v>11</v>
-      </c>
-      <c r="D130">
-        <v>5</v>
-      </c>
-      <c r="E130" t="s">
-        <v>217</v>
-      </c>
-      <c r="F130" s="2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131"/>
-      <c r="B131">
-        <v>11006</v>
-      </c>
-      <c r="C131">
-        <v>11</v>
-      </c>
-      <c r="D131">
-        <v>6</v>
-      </c>
-      <c r="E131" t="s">
-        <v>218</v>
-      </c>
-      <c r="F131" s="2">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132"/>
-      <c r="B132">
-        <v>11007</v>
-      </c>
-      <c r="C132">
-        <v>11</v>
-      </c>
-      <c r="D132">
-        <v>7</v>
-      </c>
-      <c r="E132" t="s">
-        <v>219</v>
-      </c>
-      <c r="F132" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133"/>
-      <c r="B133">
-        <v>11008</v>
-      </c>
-      <c r="C133">
-        <v>11</v>
-      </c>
-      <c r="D133">
-        <v>8</v>
-      </c>
-      <c r="E133" t="s">
-        <v>220</v>
-      </c>
-      <c r="F133" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134"/>
-      <c r="B134">
-        <v>11009</v>
-      </c>
-      <c r="C134">
-        <v>11</v>
-      </c>
-      <c r="D134">
-        <v>9</v>
-      </c>
-      <c r="E134" t="s">
-        <v>221</v>
-      </c>
-      <c r="F134" s="2">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135"/>
-      <c r="B135">
-        <v>11010</v>
-      </c>
-      <c r="C135">
-        <v>11</v>
-      </c>
-      <c r="D135">
-        <v>10</v>
-      </c>
-      <c r="E135" t="s">
-        <v>222</v>
-      </c>
-      <c r="F135" s="2">
         <v>600</v>
       </c>
     </row>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17820" windowHeight="11520"/>
+    <workbookView windowWidth="18315" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="226">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>LevelEntryNum</t>
+  </si>
+  <si>
     <t>MonsterGroup</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>关卡</t>
   </si>
   <si>
+    <t>机制数量</t>
+  </si>
+  <si>
     <t>怪物组id</t>
   </si>
   <si>
@@ -77,6 +83,9 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>10011</t>
@@ -1674,20 +1683,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G124"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="5.65" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.53333333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="4.675" style="1" customWidth="1"/>
     <col min="4" max="4" width="4.66666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.0166666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.75" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.575" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.0166666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.75" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1703,1581 +1713,1860 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G40" s="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G41" s="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G43" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G45" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G46" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G47" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G51" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G52" s="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G53" s="1">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G54" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G55" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G56" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7">
+      <c r="B57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7">
+      <c r="B58" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G58" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
+      <c r="B60" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G60" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7">
+      <c r="B62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G62" s="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7">
+      <c r="B63" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G63" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7">
+      <c r="B64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G64" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
+      <c r="B65" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G65" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
+      <c r="B66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G66" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7">
+      <c r="B68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G68" s="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7">
+      <c r="B69" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G69" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7">
+      <c r="B71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G71" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7">
+      <c r="B72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G72" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7">
+      <c r="B73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G73" s="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7">
+      <c r="B74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G74" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="B75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G75" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G76" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7">
+      <c r="B77" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G77" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
+      <c r="B78" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G78" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7">
+      <c r="B79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G79" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G80" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
+      <c r="B82" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G82" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7">
+      <c r="B83" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G83" s="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7">
+      <c r="B84" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G84" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G85" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G86" s="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7">
+      <c r="B87" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G87" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7">
+      <c r="B88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G88" s="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7">
+      <c r="B89" s="1" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G89" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7">
+      <c r="B90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G90" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7">
+      <c r="B91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G91" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G93" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G94" s="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7">
+      <c r="B95" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G95" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="B96" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G96" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="B97" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G97" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="B98" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G98" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="B99" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G99" s="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="B100" s="1" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G100" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="B101" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="2">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G101" s="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="B102" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="1">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="1">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="F102" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="1">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="1">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="2">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="1">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="1">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="1">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" s="1">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="1">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="2">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F39" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="1">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F41" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F42" s="1">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="1">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F44" s="1">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F45" s="1">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F46" s="1">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F47" s="2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F49" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F50" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" s="1">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="1">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F53" s="1">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F54" s="1">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F55" s="1">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F56" s="1">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F57" s="1">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F58" s="2">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F60" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F61" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F62" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F63" s="1">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F64" s="1">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6">
-      <c r="B65" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F65" s="1">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6">
-      <c r="B66" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="1">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6">
-      <c r="B67" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F67" s="1">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6">
-      <c r="B68" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F68" s="1">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6">
-      <c r="B69" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F69" s="2">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6">
-      <c r="B71" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F71" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6">
-      <c r="B72" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F72" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6">
-      <c r="B73" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F73" s="1">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6">
-      <c r="B74" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F74" s="1">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6">
-      <c r="B75" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F75" s="1">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6">
-      <c r="B76" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="1">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6">
-      <c r="B77" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F77" s="1">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6">
-      <c r="B78" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F78" s="1">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6">
-      <c r="B79" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F79" s="1">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6">
-      <c r="B80" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F80" s="2">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F82" s="1">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6">
-      <c r="B83" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F83" s="1">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F84" s="1">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6">
-      <c r="B85" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F85" s="1">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F86" s="1">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F87" s="1">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F88" s="1">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F89" s="1">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F90" s="1">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="91" spans="2:6">
-      <c r="B91" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F91" s="2">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F93" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F95" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6">
-      <c r="B96" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F96" s="1">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F97" s="1">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F98" s="1">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F99" s="1">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F100" s="1">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="B101" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F101" s="1">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F102" s="2">
+      <c r="G102" s="2">
         <v>530</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:7">
       <c r="A104"/>
       <c r="B104" s="2">
         <v>10001</v>
@@ -3288,14 +3577,17 @@
       <c r="D104" s="2">
         <v>1</v>
       </c>
-      <c r="E104" t="s">
-        <v>203</v>
-      </c>
-      <c r="F104" s="2">
+      <c r="E104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" t="s">
+        <v>206</v>
+      </c>
+      <c r="G104" s="2">
         <v>140</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:7">
       <c r="A105"/>
       <c r="B105" s="2">
         <v>10002</v>
@@ -3306,14 +3598,17 @@
       <c r="D105" s="2">
         <v>2</v>
       </c>
-      <c r="E105" t="s">
-        <v>204</v>
-      </c>
-      <c r="F105" s="2">
+      <c r="E105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" t="s">
+        <v>207</v>
+      </c>
+      <c r="G105" s="2">
         <v>190</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:7">
       <c r="A106"/>
       <c r="B106" s="2">
         <v>10003</v>
@@ -3324,14 +3619,17 @@
       <c r="D106" s="2">
         <v>3</v>
       </c>
-      <c r="E106" t="s">
-        <v>205</v>
-      </c>
-      <c r="F106" s="2">
+      <c r="E106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" t="s">
+        <v>208</v>
+      </c>
+      <c r="G106" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:7">
       <c r="A107"/>
       <c r="B107" s="2">
         <v>10004</v>
@@ -3342,14 +3640,17 @@
       <c r="D107" s="2">
         <v>4</v>
       </c>
-      <c r="E107" t="s">
-        <v>206</v>
-      </c>
-      <c r="F107" s="2">
+      <c r="E107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F107" t="s">
+        <v>209</v>
+      </c>
+      <c r="G107" s="2">
         <v>280</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:7">
       <c r="A108"/>
       <c r="B108" s="2">
         <v>10005</v>
@@ -3360,14 +3661,17 @@
       <c r="D108" s="2">
         <v>5</v>
       </c>
-      <c r="E108" t="s">
-        <v>207</v>
-      </c>
-      <c r="F108" s="2">
+      <c r="E108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" t="s">
+        <v>210</v>
+      </c>
+      <c r="G108" s="2">
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:7">
       <c r="A109"/>
       <c r="B109" s="2">
         <v>10006</v>
@@ -3378,14 +3682,17 @@
       <c r="D109" s="2">
         <v>6</v>
       </c>
-      <c r="E109" t="s">
-        <v>208</v>
-      </c>
-      <c r="F109" s="2">
+      <c r="E109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F109" t="s">
+        <v>211</v>
+      </c>
+      <c r="G109" s="2">
         <v>375</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:7">
       <c r="A110"/>
       <c r="B110" s="2">
         <v>10007</v>
@@ -3396,14 +3703,17 @@
       <c r="D110" s="2">
         <v>7</v>
       </c>
-      <c r="E110" t="s">
-        <v>209</v>
-      </c>
-      <c r="F110" s="2">
+      <c r="E110" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110" t="s">
+        <v>212</v>
+      </c>
+      <c r="G110" s="2">
         <v>425</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:7">
       <c r="A111"/>
       <c r="B111" s="2">
         <v>10008</v>
@@ -3414,14 +3724,17 @@
       <c r="D111" s="2">
         <v>8</v>
       </c>
-      <c r="E111" t="s">
-        <v>210</v>
-      </c>
-      <c r="F111" s="2">
+      <c r="E111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111" t="s">
+        <v>213</v>
+      </c>
+      <c r="G111" s="2">
         <v>470</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:7">
       <c r="A112"/>
       <c r="B112" s="2">
         <v>10009</v>
@@ -3432,14 +3745,17 @@
       <c r="D112" s="2">
         <v>9</v>
       </c>
-      <c r="E112" t="s">
-        <v>211</v>
-      </c>
-      <c r="F112" s="2">
+      <c r="E112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F112" t="s">
+        <v>214</v>
+      </c>
+      <c r="G112" s="2">
         <v>515</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113"/>
       <c r="B113" s="2">
         <v>10010</v>
@@ -3450,14 +3766,17 @@
       <c r="D113" s="2">
         <v>10</v>
       </c>
-      <c r="E113" t="s">
-        <v>212</v>
-      </c>
-      <c r="F113" s="2">
+      <c r="E113" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F113" t="s">
+        <v>215</v>
+      </c>
+      <c r="G113" s="2">
         <v>565</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:7">
       <c r="A115"/>
       <c r="B115" s="2">
         <v>11001</v>
@@ -3468,14 +3787,17 @@
       <c r="D115" s="2">
         <v>1</v>
       </c>
-      <c r="E115" t="s">
-        <v>213</v>
-      </c>
-      <c r="F115" s="2">
+      <c r="E115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" t="s">
+        <v>216</v>
+      </c>
+      <c r="G115" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116"/>
       <c r="B116" s="2">
         <v>11002</v>
@@ -3486,14 +3808,17 @@
       <c r="D116" s="2">
         <v>2</v>
       </c>
-      <c r="E116" t="s">
-        <v>214</v>
-      </c>
-      <c r="F116" s="2">
+      <c r="E116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F116" t="s">
+        <v>217</v>
+      </c>
+      <c r="G116" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:7">
       <c r="A117"/>
       <c r="B117" s="2">
         <v>11003</v>
@@ -3504,14 +3829,17 @@
       <c r="D117" s="2">
         <v>3</v>
       </c>
-      <c r="E117" t="s">
-        <v>215</v>
-      </c>
-      <c r="F117" s="2">
+      <c r="E117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" t="s">
+        <v>218</v>
+      </c>
+      <c r="G117" s="2">
         <v>250</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118"/>
       <c r="B118" s="2">
         <v>11004</v>
@@ -3522,14 +3850,17 @@
       <c r="D118" s="2">
         <v>4</v>
       </c>
-      <c r="E118" t="s">
-        <v>216</v>
-      </c>
-      <c r="F118" s="2">
+      <c r="E118" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" t="s">
+        <v>219</v>
+      </c>
+      <c r="G118" s="2">
         <v>300</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:7">
       <c r="A119"/>
       <c r="B119" s="2">
         <v>11005</v>
@@ -3540,14 +3871,17 @@
       <c r="D119" s="2">
         <v>5</v>
       </c>
-      <c r="E119" t="s">
-        <v>217</v>
-      </c>
-      <c r="F119" s="2">
+      <c r="E119" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" t="s">
+        <v>220</v>
+      </c>
+      <c r="G119" s="2">
         <v>350</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120"/>
       <c r="B120" s="2">
         <v>11006</v>
@@ -3558,14 +3892,17 @@
       <c r="D120" s="2">
         <v>6</v>
       </c>
-      <c r="E120" t="s">
-        <v>218</v>
-      </c>
-      <c r="F120" s="2">
+      <c r="E120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" t="s">
+        <v>221</v>
+      </c>
+      <c r="G120" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:7">
       <c r="A121"/>
       <c r="B121" s="2">
         <v>11007</v>
@@ -3576,14 +3913,17 @@
       <c r="D121" s="2">
         <v>7</v>
       </c>
-      <c r="E121" t="s">
-        <v>219</v>
-      </c>
-      <c r="F121" s="2">
+      <c r="E121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" t="s">
+        <v>222</v>
+      </c>
+      <c r="G121" s="2">
         <v>450</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:7">
       <c r="A122"/>
       <c r="B122" s="2">
         <v>11008</v>
@@ -3594,14 +3934,17 @@
       <c r="D122" s="2">
         <v>8</v>
       </c>
-      <c r="E122" t="s">
-        <v>220</v>
-      </c>
-      <c r="F122" s="2">
+      <c r="E122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F122" t="s">
+        <v>223</v>
+      </c>
+      <c r="G122" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:7">
       <c r="A123"/>
       <c r="B123" s="2">
         <v>11009</v>
@@ -3612,14 +3955,17 @@
       <c r="D123" s="2">
         <v>9</v>
       </c>
-      <c r="E123" t="s">
-        <v>221</v>
-      </c>
-      <c r="F123" s="2">
+      <c r="E123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123" t="s">
+        <v>224</v>
+      </c>
+      <c r="G123" s="2">
         <v>550</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:7">
       <c r="A124"/>
       <c r="B124" s="2">
         <v>11010</v>
@@ -3630,10 +3976,13 @@
       <c r="D124" s="2">
         <v>10</v>
       </c>
-      <c r="E124" t="s">
-        <v>222</v>
-      </c>
-      <c r="F124" s="2">
+      <c r="E124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F124" t="s">
+        <v>225</v>
+      </c>
+      <c r="G124" s="2">
         <v>600</v>
       </c>
     </row>

--- a/Config/LevelConfig.xlsx
+++ b/Config/LevelConfig.xlsx
@@ -1043,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I314"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="5.65" customWidth="1" style="1" min="1" max="1"/>
@@ -4950,6 +4950,4756 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>120011</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>180</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>12002</v>
+      </c>
+      <c r="C126" t="n">
+        <v>12</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>120021</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>240</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>12003</v>
+      </c>
+      <c r="C127" t="n">
+        <v>12</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>120031</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>300</v>
+      </c>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>12004</v>
+      </c>
+      <c r="C128" t="n">
+        <v>12</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>120041|120042</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>360</v>
+      </c>
+      <c r="H128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>12005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>12</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>120051|120052</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>415</v>
+      </c>
+      <c r="H129" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>12006</v>
+      </c>
+      <c r="C130" t="n">
+        <v>12</v>
+      </c>
+      <c r="D130" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>120061|120062</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>475</v>
+      </c>
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>12007</v>
+      </c>
+      <c r="C131" t="n">
+        <v>12</v>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>120071|120072|120073</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>535</v>
+      </c>
+      <c r="H131" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>12008</v>
+      </c>
+      <c r="C132" t="n">
+        <v>12</v>
+      </c>
+      <c r="D132" t="n">
+        <v>8</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>120081|120082|120083</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>595</v>
+      </c>
+      <c r="H132" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>12009</v>
+      </c>
+      <c r="C133" t="n">
+        <v>12</v>
+      </c>
+      <c r="D133" t="n">
+        <v>9</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>120091|120092|120093</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>655</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>12010</v>
+      </c>
+      <c r="C134" t="n">
+        <v>12</v>
+      </c>
+      <c r="D134" t="n">
+        <v>10</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>120101|120102|120103</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>715</v>
+      </c>
+      <c r="H134" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C135" t="n">
+        <v>13</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>130011</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>190</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>13002</v>
+      </c>
+      <c r="C136" t="n">
+        <v>13</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>130021</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>255</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>13003</v>
+      </c>
+      <c r="C137" t="n">
+        <v>13</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>130031</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>315</v>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>13004</v>
+      </c>
+      <c r="C138" t="n">
+        <v>13</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>130041|130042</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>380</v>
+      </c>
+      <c r="H138" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>13005</v>
+      </c>
+      <c r="C139" t="n">
+        <v>13</v>
+      </c>
+      <c r="D139" t="n">
+        <v>5</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>130051|130052</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>440</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>13006</v>
+      </c>
+      <c r="C140" t="n">
+        <v>13</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>130061|130062</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>505</v>
+      </c>
+      <c r="H140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>13007</v>
+      </c>
+      <c r="C141" t="n">
+        <v>13</v>
+      </c>
+      <c r="D141" t="n">
+        <v>7</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>130071|130072|130073</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>570</v>
+      </c>
+      <c r="H141" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>13008</v>
+      </c>
+      <c r="C142" t="n">
+        <v>13</v>
+      </c>
+      <c r="D142" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>130081|130082|130083</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>630</v>
+      </c>
+      <c r="H142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>13009</v>
+      </c>
+      <c r="C143" t="n">
+        <v>13</v>
+      </c>
+      <c r="D143" t="n">
+        <v>9</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>130091|130092|130093</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>695</v>
+      </c>
+      <c r="H143" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>13010</v>
+      </c>
+      <c r="C144" t="n">
+        <v>13</v>
+      </c>
+      <c r="D144" t="n">
+        <v>10</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>130101|130102|130103</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>760</v>
+      </c>
+      <c r="H144" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>14001</v>
+      </c>
+      <c r="C145" t="n">
+        <v>14</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>140011</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>200</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>14002</v>
+      </c>
+      <c r="C146" t="n">
+        <v>14</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>140021</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>265</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>14003</v>
+      </c>
+      <c r="C147" t="n">
+        <v>14</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>140031</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>335</v>
+      </c>
+      <c r="H147" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>14004</v>
+      </c>
+      <c r="C148" t="n">
+        <v>14</v>
+      </c>
+      <c r="D148" t="n">
+        <v>4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>140041|140042</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>400</v>
+      </c>
+      <c r="H148" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>14005</v>
+      </c>
+      <c r="C149" t="n">
+        <v>14</v>
+      </c>
+      <c r="D149" t="n">
+        <v>5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>140051|140052</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>470</v>
+      </c>
+      <c r="H149" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>14006</v>
+      </c>
+      <c r="C150" t="n">
+        <v>14</v>
+      </c>
+      <c r="D150" t="n">
+        <v>6</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>140061|140062</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>535</v>
+      </c>
+      <c r="H150" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>14007</v>
+      </c>
+      <c r="C151" t="n">
+        <v>14</v>
+      </c>
+      <c r="D151" t="n">
+        <v>7</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>140071|140072|140073</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>600</v>
+      </c>
+      <c r="H151" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>14008</v>
+      </c>
+      <c r="C152" t="n">
+        <v>14</v>
+      </c>
+      <c r="D152" t="n">
+        <v>8</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>140081|140082|140083</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>670</v>
+      </c>
+      <c r="H152" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>14009</v>
+      </c>
+      <c r="C153" t="n">
+        <v>14</v>
+      </c>
+      <c r="D153" t="n">
+        <v>9</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>140091|140092|140093</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>735</v>
+      </c>
+      <c r="H153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>14010</v>
+      </c>
+      <c r="C154" t="n">
+        <v>14</v>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>140101|140102|140103</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>800</v>
+      </c>
+      <c r="H154" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>15001</v>
+      </c>
+      <c r="C155" t="n">
+        <v>15</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>150011</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>210</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>15002</v>
+      </c>
+      <c r="C156" t="n">
+        <v>15</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>150021</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>280</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>15003</v>
+      </c>
+      <c r="C157" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>150031</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>350</v>
+      </c>
+      <c r="H157" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>15004</v>
+      </c>
+      <c r="C158" t="n">
+        <v>15</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>150041|150042</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>420</v>
+      </c>
+      <c r="H158" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>15005</v>
+      </c>
+      <c r="C159" t="n">
+        <v>15</v>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>150051|150052</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>495</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>15006</v>
+      </c>
+      <c r="C160" t="n">
+        <v>15</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>150061|150062</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>565</v>
+      </c>
+      <c r="H160" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>15007</v>
+      </c>
+      <c r="C161" t="n">
+        <v>15</v>
+      </c>
+      <c r="D161" t="n">
+        <v>7</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>150071|150072|150073</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>635</v>
+      </c>
+      <c r="H161" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>15008</v>
+      </c>
+      <c r="C162" t="n">
+        <v>15</v>
+      </c>
+      <c r="D162" t="n">
+        <v>8</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>150081|150082|150083</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>705</v>
+      </c>
+      <c r="H162" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>15009</v>
+      </c>
+      <c r="C163" t="n">
+        <v>15</v>
+      </c>
+      <c r="D163" t="n">
+        <v>9</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>150091|150092|150093</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>775</v>
+      </c>
+      <c r="H163" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C164" t="n">
+        <v>15</v>
+      </c>
+      <c r="D164" t="n">
+        <v>10</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>150101|150102|150103</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>845</v>
+      </c>
+      <c r="H164" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>16001</v>
+      </c>
+      <c r="C165" t="n">
+        <v>16</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>160011</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>220</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C166" t="n">
+        <v>16</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>160021</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>295</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>16003</v>
+      </c>
+      <c r="C167" t="n">
+        <v>16</v>
+      </c>
+      <c r="D167" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>160031</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>370</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>16004</v>
+      </c>
+      <c r="C168" t="n">
+        <v>16</v>
+      </c>
+      <c r="D168" t="n">
+        <v>4</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>160041|160042</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>445</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>16005</v>
+      </c>
+      <c r="C169" t="n">
+        <v>16</v>
+      </c>
+      <c r="D169" t="n">
+        <v>5</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>160051|160052</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>520</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>16006</v>
+      </c>
+      <c r="C170" t="n">
+        <v>16</v>
+      </c>
+      <c r="D170" t="n">
+        <v>6</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>160061|160062</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>590</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>16007</v>
+      </c>
+      <c r="C171" t="n">
+        <v>16</v>
+      </c>
+      <c r="D171" t="n">
+        <v>7</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>160071|160072|160073</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>665</v>
+      </c>
+      <c r="H171" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>16008</v>
+      </c>
+      <c r="C172" t="n">
+        <v>16</v>
+      </c>
+      <c r="D172" t="n">
+        <v>8</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>160081|160082|160083</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>740</v>
+      </c>
+      <c r="H172" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>16009</v>
+      </c>
+      <c r="C173" t="n">
+        <v>16</v>
+      </c>
+      <c r="D173" t="n">
+        <v>9</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>160091|160092|160093</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>815</v>
+      </c>
+      <c r="H173" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>16010</v>
+      </c>
+      <c r="C174" t="n">
+        <v>16</v>
+      </c>
+      <c r="D174" t="n">
+        <v>10</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>160101|160102|160103</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>890</v>
+      </c>
+      <c r="H174" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>17001</v>
+      </c>
+      <c r="C175" t="n">
+        <v>17</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>170011</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>235</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>17002</v>
+      </c>
+      <c r="C176" t="n">
+        <v>17</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>170021</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>310</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>17003</v>
+      </c>
+      <c r="C177" t="n">
+        <v>17</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>170031</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>390</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>17004</v>
+      </c>
+      <c r="C178" t="n">
+        <v>17</v>
+      </c>
+      <c r="D178" t="n">
+        <v>4</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>170041|170042</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>465</v>
+      </c>
+      <c r="H178" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>17005</v>
+      </c>
+      <c r="C179" t="n">
+        <v>17</v>
+      </c>
+      <c r="D179" t="n">
+        <v>5</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>170051|170052</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>545</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>17006</v>
+      </c>
+      <c r="C180" t="n">
+        <v>17</v>
+      </c>
+      <c r="D180" t="n">
+        <v>6</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>170061|170062</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>620</v>
+      </c>
+      <c r="H180" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>17007</v>
+      </c>
+      <c r="C181" t="n">
+        <v>17</v>
+      </c>
+      <c r="D181" t="n">
+        <v>7</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>170071|170072|170073</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>700</v>
+      </c>
+      <c r="H181" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>17008</v>
+      </c>
+      <c r="C182" t="n">
+        <v>17</v>
+      </c>
+      <c r="D182" t="n">
+        <v>8</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>170081|170082|170083</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>775</v>
+      </c>
+      <c r="H182" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>17009</v>
+      </c>
+      <c r="C183" t="n">
+        <v>17</v>
+      </c>
+      <c r="D183" t="n">
+        <v>9</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>170091|170092|170093</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>855</v>
+      </c>
+      <c r="H183" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>17010</v>
+      </c>
+      <c r="C184" t="n">
+        <v>17</v>
+      </c>
+      <c r="D184" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>170101|170102|170103</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>930</v>
+      </c>
+      <c r="H184" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>18001</v>
+      </c>
+      <c r="C185" t="n">
+        <v>18</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>180011</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>245</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>18002</v>
+      </c>
+      <c r="C186" t="n">
+        <v>18</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>180021</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>325</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>18003</v>
+      </c>
+      <c r="C187" t="n">
+        <v>18</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>180031</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>405</v>
+      </c>
+      <c r="H187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>18004</v>
+      </c>
+      <c r="C188" t="n">
+        <v>18</v>
+      </c>
+      <c r="D188" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>180041|180042</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>485</v>
+      </c>
+      <c r="H188" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>18005</v>
+      </c>
+      <c r="C189" t="n">
+        <v>18</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>180051|180052</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>570</v>
+      </c>
+      <c r="H189" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>18006</v>
+      </c>
+      <c r="C190" t="n">
+        <v>18</v>
+      </c>
+      <c r="D190" t="n">
+        <v>6</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>180061|180062</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>650</v>
+      </c>
+      <c r="H190" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>18007</v>
+      </c>
+      <c r="C191" t="n">
+        <v>18</v>
+      </c>
+      <c r="D191" t="n">
+        <v>7</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>180071|180072|180073</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>730</v>
+      </c>
+      <c r="H191" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>18008</v>
+      </c>
+      <c r="C192" t="n">
+        <v>18</v>
+      </c>
+      <c r="D192" t="n">
+        <v>8</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>180081|180082|180083</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>810</v>
+      </c>
+      <c r="H192" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>18009</v>
+      </c>
+      <c r="C193" t="n">
+        <v>18</v>
+      </c>
+      <c r="D193" t="n">
+        <v>9</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>180091|180092|180093</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>895</v>
+      </c>
+      <c r="H193" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>18010</v>
+      </c>
+      <c r="C194" t="n">
+        <v>18</v>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>180101|180102|180103</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>975</v>
+      </c>
+      <c r="H194" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>19001</v>
+      </c>
+      <c r="C195" t="n">
+        <v>19</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>190011</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>255</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>19002</v>
+      </c>
+      <c r="C196" t="n">
+        <v>19</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>190021</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>340</v>
+      </c>
+      <c r="H196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>19003</v>
+      </c>
+      <c r="C197" t="n">
+        <v>19</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>190031</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>425</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>19004</v>
+      </c>
+      <c r="C198" t="n">
+        <v>19</v>
+      </c>
+      <c r="D198" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>190041|190042</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>510</v>
+      </c>
+      <c r="H198" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>19005</v>
+      </c>
+      <c r="C199" t="n">
+        <v>19</v>
+      </c>
+      <c r="D199" t="n">
+        <v>5</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>190051|190052</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>595</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>19006</v>
+      </c>
+      <c r="C200" t="n">
+        <v>19</v>
+      </c>
+      <c r="D200" t="n">
+        <v>6</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>190061|190062</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>680</v>
+      </c>
+      <c r="H200" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>19007</v>
+      </c>
+      <c r="C201" t="n">
+        <v>19</v>
+      </c>
+      <c r="D201" t="n">
+        <v>7</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>190071|190072|190073</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>765</v>
+      </c>
+      <c r="H201" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>19008</v>
+      </c>
+      <c r="C202" t="n">
+        <v>19</v>
+      </c>
+      <c r="D202" t="n">
+        <v>8</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>190081|190082|190083</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>850</v>
+      </c>
+      <c r="H202" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>19009</v>
+      </c>
+      <c r="C203" t="n">
+        <v>19</v>
+      </c>
+      <c r="D203" t="n">
+        <v>9</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>190091|190092|190093</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>935</v>
+      </c>
+      <c r="H203" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>19010</v>
+      </c>
+      <c r="C204" t="n">
+        <v>19</v>
+      </c>
+      <c r="D204" t="n">
+        <v>10</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>190101|190102|190103</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H204" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>20001</v>
+      </c>
+      <c r="C205" t="n">
+        <v>20</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>200011</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>265</v>
+      </c>
+      <c r="H205" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C206" t="n">
+        <v>20</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>200021</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>355</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>20003</v>
+      </c>
+      <c r="C207" t="n">
+        <v>20</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>200031</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>440</v>
+      </c>
+      <c r="H207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>20004</v>
+      </c>
+      <c r="C208" t="n">
+        <v>20</v>
+      </c>
+      <c r="D208" t="n">
+        <v>4</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>200041|200042</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>530</v>
+      </c>
+      <c r="H208" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>20005</v>
+      </c>
+      <c r="C209" t="n">
+        <v>20</v>
+      </c>
+      <c r="D209" t="n">
+        <v>5</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>200051|200052</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>620</v>
+      </c>
+      <c r="H209" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>20006</v>
+      </c>
+      <c r="C210" t="n">
+        <v>20</v>
+      </c>
+      <c r="D210" t="n">
+        <v>6</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>200061|200062</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>705</v>
+      </c>
+      <c r="H210" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>20007</v>
+      </c>
+      <c r="C211" t="n">
+        <v>20</v>
+      </c>
+      <c r="D211" t="n">
+        <v>7</v>
+      </c>
+      <c r="E211" t="n">
+        <v>2</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>200071|200072|200073</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>795</v>
+      </c>
+      <c r="H211" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>20008</v>
+      </c>
+      <c r="C212" t="n">
+        <v>20</v>
+      </c>
+      <c r="D212" t="n">
+        <v>8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>200081|200082|200083</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>885</v>
+      </c>
+      <c r="H212" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>20009</v>
+      </c>
+      <c r="C213" t="n">
+        <v>20</v>
+      </c>
+      <c r="D213" t="n">
+        <v>9</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>200091|200092|200093</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>970</v>
+      </c>
+      <c r="H213" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>20010</v>
+      </c>
+      <c r="C214" t="n">
+        <v>20</v>
+      </c>
+      <c r="D214" t="n">
+        <v>10</v>
+      </c>
+      <c r="E214" t="n">
+        <v>3</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>200101|200102|200103</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>1060</v>
+      </c>
+      <c r="H214" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>21001</v>
+      </c>
+      <c r="C215" t="n">
+        <v>21</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>210011</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>275</v>
+      </c>
+      <c r="H215" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>21002</v>
+      </c>
+      <c r="C216" t="n">
+        <v>21</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>210021</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>370</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>21003</v>
+      </c>
+      <c r="C217" t="n">
+        <v>21</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>210031</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>460</v>
+      </c>
+      <c r="H217" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>21004</v>
+      </c>
+      <c r="C218" t="n">
+        <v>21</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>210041|210042</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>550</v>
+      </c>
+      <c r="H218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C219" t="n">
+        <v>21</v>
+      </c>
+      <c r="D219" t="n">
+        <v>5</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>210051|210052</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>645</v>
+      </c>
+      <c r="H219" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>21006</v>
+      </c>
+      <c r="C220" t="n">
+        <v>21</v>
+      </c>
+      <c r="D220" t="n">
+        <v>6</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>210061|210062</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>735</v>
+      </c>
+      <c r="H220" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>21007</v>
+      </c>
+      <c r="C221" t="n">
+        <v>21</v>
+      </c>
+      <c r="D221" t="n">
+        <v>7</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>210071|210072|210073</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>830</v>
+      </c>
+      <c r="H221" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>21008</v>
+      </c>
+      <c r="C222" t="n">
+        <v>21</v>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>210081|210082|210083</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>920</v>
+      </c>
+      <c r="H222" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>21009</v>
+      </c>
+      <c r="C223" t="n">
+        <v>21</v>
+      </c>
+      <c r="D223" t="n">
+        <v>9</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>210091|210092|210093</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H223" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>21010</v>
+      </c>
+      <c r="C224" t="n">
+        <v>21</v>
+      </c>
+      <c r="D224" t="n">
+        <v>10</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>210101|210102|210103</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1105</v>
+      </c>
+      <c r="H224" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>22001</v>
+      </c>
+      <c r="C225" t="n">
+        <v>22</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>220011</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>285</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>22002</v>
+      </c>
+      <c r="C226" t="n">
+        <v>22</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>220021</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>380</v>
+      </c>
+      <c r="H226" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>22003</v>
+      </c>
+      <c r="C227" t="n">
+        <v>22</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>220031</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>480</v>
+      </c>
+      <c r="H227" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>22004</v>
+      </c>
+      <c r="C228" t="n">
+        <v>22</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>220041|220042</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>575</v>
+      </c>
+      <c r="H228" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>22005</v>
+      </c>
+      <c r="C229" t="n">
+        <v>22</v>
+      </c>
+      <c r="D229" t="n">
+        <v>5</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>220051|220052</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>670</v>
+      </c>
+      <c r="H229" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>22006</v>
+      </c>
+      <c r="C230" t="n">
+        <v>22</v>
+      </c>
+      <c r="D230" t="n">
+        <v>6</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>220061|220062</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>765</v>
+      </c>
+      <c r="H230" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>22007</v>
+      </c>
+      <c r="C231" t="n">
+        <v>22</v>
+      </c>
+      <c r="D231" t="n">
+        <v>7</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>220071|220072|220073</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>860</v>
+      </c>
+      <c r="H231" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>22008</v>
+      </c>
+      <c r="C232" t="n">
+        <v>22</v>
+      </c>
+      <c r="D232" t="n">
+        <v>8</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>220081|220082|220083</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>955</v>
+      </c>
+      <c r="H232" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>22009</v>
+      </c>
+      <c r="C233" t="n">
+        <v>22</v>
+      </c>
+      <c r="D233" t="n">
+        <v>9</v>
+      </c>
+      <c r="E233" t="n">
+        <v>2</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>220091|220092|220093</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H233" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>22010</v>
+      </c>
+      <c r="C234" t="n">
+        <v>22</v>
+      </c>
+      <c r="D234" t="n">
+        <v>10</v>
+      </c>
+      <c r="E234" t="n">
+        <v>3</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>220101|220102|220103</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>1145</v>
+      </c>
+      <c r="H234" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>23001</v>
+      </c>
+      <c r="C235" t="n">
+        <v>23</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>230011</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>300</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>23002</v>
+      </c>
+      <c r="C236" t="n">
+        <v>23</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>230021</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>395</v>
+      </c>
+      <c r="H236" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>23003</v>
+      </c>
+      <c r="C237" t="n">
+        <v>23</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>230031</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>495</v>
+      </c>
+      <c r="H237" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>23004</v>
+      </c>
+      <c r="C238" t="n">
+        <v>23</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>230041|230042</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>595</v>
+      </c>
+      <c r="H238" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>23005</v>
+      </c>
+      <c r="C239" t="n">
+        <v>23</v>
+      </c>
+      <c r="D239" t="n">
+        <v>5</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>230051|230052</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>695</v>
+      </c>
+      <c r="H239" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>23006</v>
+      </c>
+      <c r="C240" t="n">
+        <v>23</v>
+      </c>
+      <c r="D240" t="n">
+        <v>6</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>230061|230062</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>795</v>
+      </c>
+      <c r="H240" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>23007</v>
+      </c>
+      <c r="C241" t="n">
+        <v>23</v>
+      </c>
+      <c r="D241" t="n">
+        <v>7</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>230071|230072|230073</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>895</v>
+      </c>
+      <c r="H241" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>23008</v>
+      </c>
+      <c r="C242" t="n">
+        <v>23</v>
+      </c>
+      <c r="D242" t="n">
+        <v>8</v>
+      </c>
+      <c r="E242" t="n">
+        <v>2</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>230081|230082|230083</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>990</v>
+      </c>
+      <c r="H242" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>23009</v>
+      </c>
+      <c r="C243" t="n">
+        <v>23</v>
+      </c>
+      <c r="D243" t="n">
+        <v>9</v>
+      </c>
+      <c r="E243" t="n">
+        <v>2</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>230091|230092|230093</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>1090</v>
+      </c>
+      <c r="H243" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>23010</v>
+      </c>
+      <c r="C244" t="n">
+        <v>23</v>
+      </c>
+      <c r="D244" t="n">
+        <v>10</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>230101|230102|230103</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H244" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>24001</v>
+      </c>
+      <c r="C245" t="n">
+        <v>24</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>240011</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>310</v>
+      </c>
+      <c r="H245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>24002</v>
+      </c>
+      <c r="C246" t="n">
+        <v>24</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>240021</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>410</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>24003</v>
+      </c>
+      <c r="C247" t="n">
+        <v>24</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>240031</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>515</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>24004</v>
+      </c>
+      <c r="C248" t="n">
+        <v>24</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>240041|240042</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>615</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>24005</v>
+      </c>
+      <c r="C249" t="n">
+        <v>24</v>
+      </c>
+      <c r="D249" t="n">
+        <v>5</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>240051|240052</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>720</v>
+      </c>
+      <c r="H249" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>24006</v>
+      </c>
+      <c r="C250" t="n">
+        <v>24</v>
+      </c>
+      <c r="D250" t="n">
+        <v>6</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>240061|240062</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>820</v>
+      </c>
+      <c r="H250" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>24007</v>
+      </c>
+      <c r="C251" t="n">
+        <v>24</v>
+      </c>
+      <c r="D251" t="n">
+        <v>7</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>240071|240072|240073</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>925</v>
+      </c>
+      <c r="H251" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>24008</v>
+      </c>
+      <c r="C252" t="n">
+        <v>24</v>
+      </c>
+      <c r="D252" t="n">
+        <v>8</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>240081|240082|240083</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H252" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>24009</v>
+      </c>
+      <c r="C253" t="n">
+        <v>24</v>
+      </c>
+      <c r="D253" t="n">
+        <v>9</v>
+      </c>
+      <c r="E253" t="n">
+        <v>2</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>240091|240092|240093</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>1130</v>
+      </c>
+      <c r="H253" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>24010</v>
+      </c>
+      <c r="C254" t="n">
+        <v>24</v>
+      </c>
+      <c r="D254" t="n">
+        <v>10</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>240101|240102|240103</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>1235</v>
+      </c>
+      <c r="H254" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>25001</v>
+      </c>
+      <c r="C255" t="n">
+        <v>25</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>250011</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>320</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>25002</v>
+      </c>
+      <c r="C256" t="n">
+        <v>25</v>
+      </c>
+      <c r="D256" t="n">
+        <v>2</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>250021</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>425</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>25003</v>
+      </c>
+      <c r="C257" t="n">
+        <v>25</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>250031</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>530</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>25004</v>
+      </c>
+      <c r="C258" t="n">
+        <v>25</v>
+      </c>
+      <c r="D258" t="n">
+        <v>4</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>250041|250042</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>640</v>
+      </c>
+      <c r="H258" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>25005</v>
+      </c>
+      <c r="C259" t="n">
+        <v>25</v>
+      </c>
+      <c r="D259" t="n">
+        <v>5</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>250051|250052</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>745</v>
+      </c>
+      <c r="H259" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>25006</v>
+      </c>
+      <c r="C260" t="n">
+        <v>25</v>
+      </c>
+      <c r="D260" t="n">
+        <v>6</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>250061|250062</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>850</v>
+      </c>
+      <c r="H260" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>25007</v>
+      </c>
+      <c r="C261" t="n">
+        <v>25</v>
+      </c>
+      <c r="D261" t="n">
+        <v>7</v>
+      </c>
+      <c r="E261" t="n">
+        <v>2</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>250071|250072|250073</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>960</v>
+      </c>
+      <c r="H261" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>25008</v>
+      </c>
+      <c r="C262" t="n">
+        <v>25</v>
+      </c>
+      <c r="D262" t="n">
+        <v>8</v>
+      </c>
+      <c r="E262" t="n">
+        <v>2</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>250081|250082|250083</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H262" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>25009</v>
+      </c>
+      <c r="C263" t="n">
+        <v>25</v>
+      </c>
+      <c r="D263" t="n">
+        <v>9</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>250091|250092|250093</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>1170</v>
+      </c>
+      <c r="H263" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>25010</v>
+      </c>
+      <c r="C264" t="n">
+        <v>25</v>
+      </c>
+      <c r="D264" t="n">
+        <v>10</v>
+      </c>
+      <c r="E264" t="n">
+        <v>3</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>250101|250102|250103</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>1275</v>
+      </c>
+      <c r="H264" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>26001</v>
+      </c>
+      <c r="C265" t="n">
+        <v>26</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>260011</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>330</v>
+      </c>
+      <c r="H265" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>26002</v>
+      </c>
+      <c r="C266" t="n">
+        <v>26</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>260021</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>440</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>26003</v>
+      </c>
+      <c r="C267" t="n">
+        <v>26</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>260031</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>550</v>
+      </c>
+      <c r="H267" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>26004</v>
+      </c>
+      <c r="C268" t="n">
+        <v>26</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>260041|260042</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>660</v>
+      </c>
+      <c r="H268" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>26005</v>
+      </c>
+      <c r="C269" t="n">
+        <v>26</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>260051|260052</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>770</v>
+      </c>
+      <c r="H269" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>26006</v>
+      </c>
+      <c r="C270" t="n">
+        <v>26</v>
+      </c>
+      <c r="D270" t="n">
+        <v>6</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>260061|260062</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>880</v>
+      </c>
+      <c r="H270" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>26007</v>
+      </c>
+      <c r="C271" t="n">
+        <v>26</v>
+      </c>
+      <c r="D271" t="n">
+        <v>7</v>
+      </c>
+      <c r="E271" t="n">
+        <v>2</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>260071|260072|260073</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>990</v>
+      </c>
+      <c r="H271" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>26008</v>
+      </c>
+      <c r="C272" t="n">
+        <v>26</v>
+      </c>
+      <c r="D272" t="n">
+        <v>8</v>
+      </c>
+      <c r="E272" t="n">
+        <v>2</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>260081|260082|260083</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H272" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>26009</v>
+      </c>
+      <c r="C273" t="n">
+        <v>26</v>
+      </c>
+      <c r="D273" t="n">
+        <v>9</v>
+      </c>
+      <c r="E273" t="n">
+        <v>2</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>260091|260092|260093</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H273" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>26010</v>
+      </c>
+      <c r="C274" t="n">
+        <v>26</v>
+      </c>
+      <c r="D274" t="n">
+        <v>10</v>
+      </c>
+      <c r="E274" t="n">
+        <v>3</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>260101|260102|260103</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H274" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>27001</v>
+      </c>
+      <c r="C275" t="n">
+        <v>27</v>
+      </c>
+      <c r="D275" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>270011</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>340</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>27002</v>
+      </c>
+      <c r="C276" t="n">
+        <v>27</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>270021</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>455</v>
+      </c>
+      <c r="H276" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>27003</v>
+      </c>
+      <c r="C277" t="n">
+        <v>27</v>
+      </c>
+      <c r="D277" t="n">
+        <v>3</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>270031</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>570</v>
+      </c>
+      <c r="H277" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>27004</v>
+      </c>
+      <c r="C278" t="n">
+        <v>27</v>
+      </c>
+      <c r="D278" t="n">
+        <v>4</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>270041|270042</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>680</v>
+      </c>
+      <c r="H278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>27005</v>
+      </c>
+      <c r="C279" t="n">
+        <v>27</v>
+      </c>
+      <c r="D279" t="n">
+        <v>5</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>270051|270052</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>795</v>
+      </c>
+      <c r="H279" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>27006</v>
+      </c>
+      <c r="C280" t="n">
+        <v>27</v>
+      </c>
+      <c r="D280" t="n">
+        <v>6</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>270061|270062</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>910</v>
+      </c>
+      <c r="H280" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>27007</v>
+      </c>
+      <c r="C281" t="n">
+        <v>27</v>
+      </c>
+      <c r="D281" t="n">
+        <v>7</v>
+      </c>
+      <c r="E281" t="n">
+        <v>2</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>270071|270072|270073</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H281" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>27008</v>
+      </c>
+      <c r="C282" t="n">
+        <v>27</v>
+      </c>
+      <c r="D282" t="n">
+        <v>8</v>
+      </c>
+      <c r="E282" t="n">
+        <v>2</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>270081|270082|270083</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>1135</v>
+      </c>
+      <c r="H282" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>27009</v>
+      </c>
+      <c r="C283" t="n">
+        <v>27</v>
+      </c>
+      <c r="D283" t="n">
+        <v>9</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>270091|270092|270093</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H283" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>27010</v>
+      </c>
+      <c r="C284" t="n">
+        <v>27</v>
+      </c>
+      <c r="D284" t="n">
+        <v>10</v>
+      </c>
+      <c r="E284" t="n">
+        <v>3</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>270101|270102|270103</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>1365</v>
+      </c>
+      <c r="H284" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>28001</v>
+      </c>
+      <c r="C285" t="n">
+        <v>28</v>
+      </c>
+      <c r="D285" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>280011</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>350</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>28002</v>
+      </c>
+      <c r="C286" t="n">
+        <v>28</v>
+      </c>
+      <c r="D286" t="n">
+        <v>2</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>280021</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>470</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>28003</v>
+      </c>
+      <c r="C287" t="n">
+        <v>28</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>280031</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>585</v>
+      </c>
+      <c r="H287" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>28004</v>
+      </c>
+      <c r="C288" t="n">
+        <v>28</v>
+      </c>
+      <c r="D288" t="n">
+        <v>4</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>280041|280042</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>705</v>
+      </c>
+      <c r="H288" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>28005</v>
+      </c>
+      <c r="C289" t="n">
+        <v>28</v>
+      </c>
+      <c r="D289" t="n">
+        <v>5</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>280051|280052</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>820</v>
+      </c>
+      <c r="H289" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>28006</v>
+      </c>
+      <c r="C290" t="n">
+        <v>28</v>
+      </c>
+      <c r="D290" t="n">
+        <v>6</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>280061|280062</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>940</v>
+      </c>
+      <c r="H290" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>28007</v>
+      </c>
+      <c r="C291" t="n">
+        <v>28</v>
+      </c>
+      <c r="D291" t="n">
+        <v>7</v>
+      </c>
+      <c r="E291" t="n">
+        <v>2</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>280071|280072|280073</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>1055</v>
+      </c>
+      <c r="H291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>28008</v>
+      </c>
+      <c r="C292" t="n">
+        <v>28</v>
+      </c>
+      <c r="D292" t="n">
+        <v>8</v>
+      </c>
+      <c r="E292" t="n">
+        <v>2</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>280081|280082|280083</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>1170</v>
+      </c>
+      <c r="H292" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>28009</v>
+      </c>
+      <c r="C293" t="n">
+        <v>28</v>
+      </c>
+      <c r="D293" t="n">
+        <v>9</v>
+      </c>
+      <c r="E293" t="n">
+        <v>2</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>280091|280092|280093</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>1290</v>
+      </c>
+      <c r="H293" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>28010</v>
+      </c>
+      <c r="C294" t="n">
+        <v>28</v>
+      </c>
+      <c r="D294" t="n">
+        <v>10</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>280101|280102|280103</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>1405</v>
+      </c>
+      <c r="H294" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>29001</v>
+      </c>
+      <c r="C295" t="n">
+        <v>29</v>
+      </c>
+      <c r="D295" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>290011</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>360</v>
+      </c>
+      <c r="H295" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>29002</v>
+      </c>
+      <c r="C296" t="n">
+        <v>29</v>
+      </c>
+      <c r="D296" t="n">
+        <v>2</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>290021</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>485</v>
+      </c>
+      <c r="H296" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>29003</v>
+      </c>
+      <c r="C297" t="n">
+        <v>29</v>
+      </c>
+      <c r="D297" t="n">
+        <v>3</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>290031</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>605</v>
+      </c>
+      <c r="H297" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>29004</v>
+      </c>
+      <c r="C298" t="n">
+        <v>29</v>
+      </c>
+      <c r="D298" t="n">
+        <v>4</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>290041|290042</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>725</v>
+      </c>
+      <c r="H298" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>29005</v>
+      </c>
+      <c r="C299" t="n">
+        <v>29</v>
+      </c>
+      <c r="D299" t="n">
+        <v>5</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>290051|290052</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>845</v>
+      </c>
+      <c r="H299" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>29006</v>
+      </c>
+      <c r="C300" t="n">
+        <v>29</v>
+      </c>
+      <c r="D300" t="n">
+        <v>6</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>290061|290062</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>965</v>
+      </c>
+      <c r="H300" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>29007</v>
+      </c>
+      <c r="C301" t="n">
+        <v>29</v>
+      </c>
+      <c r="D301" t="n">
+        <v>7</v>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>290071|290072|290073</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>1085</v>
+      </c>
+      <c r="H301" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>29008</v>
+      </c>
+      <c r="C302" t="n">
+        <v>29</v>
+      </c>
+      <c r="D302" t="n">
+        <v>8</v>
+      </c>
+      <c r="E302" t="n">
+        <v>2</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>290081|290082|290083</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H302" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>29009</v>
+      </c>
+      <c r="C303" t="n">
+        <v>29</v>
+      </c>
+      <c r="D303" t="n">
+        <v>9</v>
+      </c>
+      <c r="E303" t="n">
+        <v>2</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>290091|290092|290093</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>1330</v>
+      </c>
+      <c r="H303" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>29010</v>
+      </c>
+      <c r="C304" t="n">
+        <v>29</v>
+      </c>
+      <c r="D304" t="n">
+        <v>10</v>
+      </c>
+      <c r="E304" t="n">
+        <v>3</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>290101|290102|290103</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H304" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>30001</v>
+      </c>
+      <c r="C305" t="n">
+        <v>30</v>
+      </c>
+      <c r="D305" t="n">
+        <v>1</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>300011</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>375</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>30002</v>
+      </c>
+      <c r="C306" t="n">
+        <v>30</v>
+      </c>
+      <c r="D306" t="n">
+        <v>2</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>300021</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>500</v>
+      </c>
+      <c r="H306" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C307" t="n">
+        <v>30</v>
+      </c>
+      <c r="D307" t="n">
+        <v>3</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>300031</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>620</v>
+      </c>
+      <c r="H307" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>30004</v>
+      </c>
+      <c r="C308" t="n">
+        <v>30</v>
+      </c>
+      <c r="D308" t="n">
+        <v>4</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>300041|300042</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>745</v>
+      </c>
+      <c r="H308" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C309" t="n">
+        <v>30</v>
+      </c>
+      <c r="D309" t="n">
+        <v>5</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>300051|300052</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>870</v>
+      </c>
+      <c r="H309" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C310" t="n">
+        <v>30</v>
+      </c>
+      <c r="D310" t="n">
+        <v>6</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>300061|300062</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>995</v>
+      </c>
+      <c r="H310" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C311" t="n">
+        <v>30</v>
+      </c>
+      <c r="D311" t="n">
+        <v>7</v>
+      </c>
+      <c r="E311" t="n">
+        <v>2</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>300071|300072|300073</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>1120</v>
+      </c>
+      <c r="H311" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C312" t="n">
+        <v>30</v>
+      </c>
+      <c r="D312" t="n">
+        <v>8</v>
+      </c>
+      <c r="E312" t="n">
+        <v>2</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>300081|300082|300083</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1245</v>
+      </c>
+      <c r="H312" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>30009</v>
+      </c>
+      <c r="C313" t="n">
+        <v>30</v>
+      </c>
+      <c r="D313" t="n">
+        <v>9</v>
+      </c>
+      <c r="E313" t="n">
+        <v>2</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>300091|300092|300093</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>1370</v>
+      </c>
+      <c r="H313" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C314" t="n">
+        <v>30</v>
+      </c>
+      <c r="D314" t="n">
+        <v>10</v>
+      </c>
+      <c r="E314" t="n">
+        <v>3</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>300101|300102|300103</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>1495</v>
+      </c>
+      <c r="H314" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
